--- a/api/templates/xdr_devices_summary/pk/en.xlsx
+++ b/api/templates/xdr_devices_summary/pk/en.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PROJECTS_2020\SystemOne\aspect-2\api\templates\xdr_devices_summary\bd\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PROJECTS_2020\SystemOne\aspect-2\api\templates\xdr_devices_summary\pk\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -315,6 +315,7 @@
     <xf numFmtId="9" fontId="1" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -330,11 +331,10 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -671,7 +671,7 @@
       </c>
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A2" s="14" t="s">
+      <c r="A2" s="8" t="s">
         <v>28</v>
       </c>
     </row>
@@ -684,38 +684,38 @@
       </c>
     </row>
     <row r="5" spans="1:17" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A5" s="10" t="s">
+      <c r="A5" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="B5" s="12" t="s">
+      <c r="B5" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="C5" s="12" t="s">
+      <c r="C5" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="D5" s="12" t="s">
+      <c r="D5" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="E5" s="8" t="s">
+      <c r="E5" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="F5" s="9"/>
-      <c r="G5" s="8" t="s">
+      <c r="F5" s="10"/>
+      <c r="G5" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="H5" s="9"/>
-      <c r="I5" s="8" t="s">
+      <c r="H5" s="10"/>
+      <c r="I5" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="J5" s="9"/>
-      <c r="K5" s="8" t="s">
+      <c r="J5" s="10"/>
+      <c r="K5" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="L5" s="9"/>
-      <c r="M5" s="8" t="s">
+      <c r="L5" s="10"/>
+      <c r="M5" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="N5" s="9"/>
+      <c r="N5" s="10"/>
       <c r="O5" s="2" t="s">
         <v>10</v>
       </c>
@@ -727,10 +727,10 @@
       </c>
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A6" s="11"/>
-      <c r="B6" s="15"/>
-      <c r="C6" s="15"/>
-      <c r="D6" s="13"/>
+      <c r="A6" s="12"/>
+      <c r="B6" s="14"/>
+      <c r="C6" s="14"/>
+      <c r="D6" s="15"/>
       <c r="E6" s="3" t="s">
         <v>13</v>
       </c>
@@ -788,35 +788,35 @@
         <v>20</v>
       </c>
       <c r="F7" s="6" t="e">
-        <f>IF(C7&gt;0, E7/C7, 0)</f>
+        <f>IF(D7&gt;0, E7/D7, 0)</f>
         <v>#VALUE!</v>
       </c>
       <c r="G7" t="s">
         <v>21</v>
       </c>
       <c r="H7" s="6" t="e">
-        <f>IF(C7&gt;0, G7/C7, 0)</f>
+        <f>IF(D7&gt;0, G7/D7, 0)</f>
         <v>#VALUE!</v>
       </c>
       <c r="I7" t="s">
         <v>22</v>
       </c>
       <c r="J7" s="6" t="e">
-        <f>IF(C7&gt;0, I7/C7, 0)</f>
+        <f>IF(D7&gt;0, I7/D7, 0)</f>
         <v>#VALUE!</v>
       </c>
       <c r="K7" t="s">
         <v>23</v>
       </c>
       <c r="L7" s="6" t="e">
-        <f>IF(C7&gt;0, K7/C7, 0)</f>
+        <f>IF(D7&gt;0, K7/D7, 0)</f>
         <v>#VALUE!</v>
       </c>
       <c r="M7" t="s">
         <v>24</v>
       </c>
       <c r="N7" s="6" t="e">
-        <f>IF(C7&gt;0, M7/C7, 0)</f>
+        <f>IF(D7&gt;0, M7/D7, 0)</f>
         <v>#VALUE!</v>
       </c>
       <c r="O7" t="s">
